--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486394_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486394_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7041</v>
+        <v>5.1686</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4319</v>
+        <v>4.5437</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2722</v>
+        <v>0.6249</v>
       </c>
       <c r="G2" t="n">
         <v>2.9451</v>
@@ -610,13 +610,13 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5839</v>
+        <v>0.0484</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5804</v>
+        <v>-0.4687</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1643</v>
+        <v>0.517</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7476</v>
+        <v>2.6658</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4851</v>
+        <v>2.2183</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2625</v>
+        <v>0.4474</v>
       </c>
       <c r="G3" t="n">
         <v>0.3043</v>
@@ -688,13 +688,13 @@
         <v>3.0451</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4691</v>
+        <v>-0.551</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0853</v>
+        <v>-0.3521</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3838</v>
+        <v>-0.1989</v>
       </c>
       <c r="V3" t="n">
         <v>2.2599</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.064</v>
+        <v>2.2635</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4973</v>
+        <v>1.7894</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5667</v>
+        <v>0.4742</v>
       </c>
       <c r="G4" t="n">
         <v>3.1307</v>
@@ -766,13 +766,13 @@
         <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8067</v>
+        <v>-0.6072</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7054</v>
+        <v>-0.4134</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1013</v>
+        <v>-0.1938</v>
       </c>
       <c r="V4" t="n">
         <v>-1.13</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1839</v>
+        <v>0.4471</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2049</v>
+        <v>0.497</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3889</v>
+        <v>-0.0498</v>
       </c>
       <c r="G5" t="n">
         <v>0.0232</v>
@@ -844,13 +844,13 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8819</v>
+        <v>-0.2509</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7294</v>
+        <v>-0.4374</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1525</v>
+        <v>0.1866</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1952</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BOMBINO PARADA</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6855</v>
+        <v>-0.768</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.52</v>
+        <v>-1.6696</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1656</v>
+        <v>0.9016</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.5037</v>
+        <v>-1.3216</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.1475</v>
+        <v>-0.7638</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3562</v>
+        <v>-0.5578</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.682</v>
+        <v>-0.0655</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.6636</v>
+        <v>0.219</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0183</v>
+        <v>-0.2844</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8217</v>
+        <v>-1.2561</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4838</v>
+        <v>-0.9827</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3379</v>
+        <v>-0.2733</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.435</v>
+        <v>2.3926</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>2.6101</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6234</v>
+        <v>-0.9043</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5997</v>
+        <v>-0.8424</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0238</v>
+        <v>-0.0619</v>
       </c>
       <c r="V6" t="n">
-        <v>2.6297</v>
+        <v>-0.9347</v>
       </c>
       <c r="W6" t="n">
-        <v>3.9549</v>
+        <v>-0.5443</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3252</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>P. BOMBINO PARADA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8296</v>
+        <v>-1.1942</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6696</v>
+        <v>-0.967</v>
       </c>
       <c r="F7" t="n">
-        <v>0.84</v>
+        <v>-0.2272</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3216</v>
+        <v>-3.5037</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7638</v>
+        <v>-3.1475</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5578</v>
+        <v>-0.3562</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0655</v>
+        <v>-2.682</v>
       </c>
       <c r="K7" t="n">
-        <v>0.219</v>
+        <v>-2.6636</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2844</v>
+        <v>-0.0183</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2561</v>
+        <v>-0.8217</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9827</v>
+        <v>-0.4838</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2733</v>
+        <v>-0.3379</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3926</v>
+        <v>-0.435</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R7" t="n">
-        <v>2.6101</v>
+        <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9659</v>
+        <v>0.1148</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8424</v>
+        <v>0.1526</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1235</v>
+        <v>-0.0379</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9347</v>
+        <v>2.6297</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.5443</v>
+        <v>3.9549</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3904</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3745</v>
+        <v>-1.2559</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.0924</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2866</v>
+        <v>-1.3482</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9467</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6251</v>
+        <v>-0.5065</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8904</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2653</v>
+        <v>0.2037</v>
       </c>
       <c r="V8" t="n">
         <v>-1.3252</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.61</v>
+        <v>-2.1524</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0232</v>
+        <v>-1.8429</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5868</v>
+        <v>-0.3094</v>
       </c>
       <c r="G9" t="n">
         <v>0.0537</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6611</v>
+        <v>-0.2034</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4554</v>
+        <v>-0.2752</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2056</v>
+        <v>0.0718</v>
       </c>
       <c r="V9" t="n">
         <v>1.695</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4.832200000000002</v>
+        <v>5.1745</v>
       </c>
       <c r="E10" t="n">
-        <v>4.318499999999999</v>
+        <v>4.661300000000001</v>
       </c>
       <c r="F10" t="n">
         <v>0.5135000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>16.3131</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.2025</v>
+        <v>-2.8601</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.689000000000001</v>
+        <v>-3.3468</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4866999999999999</v>
+        <v>0.4866</v>
       </c>
       <c r="V10" t="n">
         <v>2.9995</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.4556</v>
+        <v>3.6069</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4863</v>
+        <v>1.7316</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9693</v>
+        <v>1.8754</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1337</v>
+        <v>1.968</v>
       </c>
       <c r="H11" t="n">
-        <v>1.156</v>
+        <v>-0.9429</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0224</v>
+        <v>2.9109</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1578</v>
+        <v>2.3737</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9283</v>
+        <v>-1.0886</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2295</v>
+        <v>3.4624</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0241</v>
+        <v>-0.4057</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2277</v>
+        <v>0.1457</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2519</v>
+        <v>-0.5514</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4801</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9766</v>
+        <v>1.0734</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7232</v>
+        <v>0.0973</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2534</v>
+        <v>0.9761</v>
       </c>
       <c r="V11" t="n">
-        <v>2.0854</v>
+        <v>-0.7395</v>
       </c>
       <c r="W11" t="n">
-        <v>2.0854</v>
+        <v>-0.7395</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.8075</v>
+        <v>3.3727</v>
       </c>
       <c r="E12" t="n">
         <v>3.03</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2225</v>
+        <v>0.3427</v>
       </c>
       <c r="G12" t="n">
         <v>1.7443</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>0.781</v>
+        <v>1.3462</v>
       </c>
       <c r="T12" t="n">
         <v>0.0277</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7533</v>
+        <v>1.3185</v>
       </c>
       <c r="V12" t="n">
         <v>0.9347</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.7064</v>
+        <v>2.5141</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3963</v>
+        <v>0.257</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3101</v>
+        <v>2.2571</v>
       </c>
       <c r="G13" t="n">
-        <v>1.968</v>
+        <v>0.1337</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9429</v>
+        <v>1.156</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9109</v>
+        <v>-1.0224</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3737</v>
+        <v>1.1578</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.0886</v>
+        <v>0.9283</v>
       </c>
       <c r="L13" t="n">
-        <v>3.4624</v>
+        <v>0.2295</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4057</v>
+        <v>-1.0241</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1457</v>
+        <v>0.2277</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5514</v>
+        <v>-1.2519</v>
       </c>
       <c r="P13" t="n">
-        <v>1.305</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.4801</v>
       </c>
       <c r="R13" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1729</v>
+        <v>2.0351</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2379</v>
+        <v>0.4939</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4108</v>
+        <v>1.5412</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.7395</v>
+        <v>2.0854</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.7395</v>
+        <v>2.0854</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4378</v>
+        <v>1.9644</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7565</v>
+        <v>2.98</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3187</v>
+        <v>-1.0156</v>
       </c>
       <c r="G14" t="n">
         <v>1.8473</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3443</v>
+        <v>0.1824</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.5299</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4092</v>
+        <v>0.7123</v>
       </c>
       <c r="V14" t="n">
         <v>0.3698</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3511</v>
+        <v>1.8892</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5544</v>
+        <v>0.6662</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7967</v>
+        <v>1.2231</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6589</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.077</v>
+        <v>0.4612</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.113</v>
+        <v>-0.0012</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0359</v>
+        <v>0.4623</v>
       </c>
       <c r="V15" t="n">
         <v>1.8695</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. LOPEZ BARRANTES</t>
+          <t>J. GRANGER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5058</v>
+        <v>0.3819</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0515</v>
+        <v>-0.9564</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5457</v>
+        <v>1.3384</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2955</v>
+        <v>-2.2734</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6995</v>
+        <v>-1.3108</v>
       </c>
       <c r="I16" t="n">
-        <v>0.596</v>
+        <v>-0.9626</v>
       </c>
       <c r="J16" t="n">
-        <v>0.584</v>
+        <v>-1.0667</v>
       </c>
       <c r="K16" t="n">
-        <v>0.584</v>
+        <v>-1.356</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.2893</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7116</v>
+        <v>-1.2066</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1155</v>
+        <v>0.0452</v>
       </c>
       <c r="O16" t="n">
-        <v>0.596</v>
+        <v>-1.2519</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>-1.305</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8512</v>
+        <v>1.4601</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5396</v>
+        <v>0.0901</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3116</v>
+        <v>1.3699</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.13</v>
+        <v>0.7602</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GRANGER</t>
+          <t>H. LOPEZ BARRANTES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8847</v>
+        <v>-1.1686</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.627</v>
+        <v>-1.4986</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7423</v>
+        <v>0.33</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2734</v>
+        <v>1.2955</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3108</v>
+        <v>0.6995</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9626</v>
+        <v>0.596</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0667</v>
+        <v>0.584</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.356</v>
+        <v>0.584</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2893</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2066</v>
+        <v>0.7116</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0452</v>
+        <v>0.1155</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2519</v>
+        <v>0.596</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1935</v>
+        <v>0.1884</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5804</v>
+        <v>0.0925</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7739</v>
+        <v>0.0958</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7602</v>
+        <v>-1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5047</v>
+        <v>-1.2941</v>
       </c>
       <c r="E18" t="n">
         <v>-1.2789</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2259</v>
+        <v>-0.0152</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2408</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1764</v>
+        <v>0.0342</v>
       </c>
       <c r="T18" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1079</v>
+        <v>0.1027</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.2291</v>
+        <v>-3.5409</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0769</v>
+        <v>-2.3073</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1522</v>
+        <v>-1.2336</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3116</v>
+        <v>-1.6161</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7578</v>
+        <v>2.2415</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0694</v>
+        <v>-3.8576</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6271</v>
+        <v>-0.8598</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2957</v>
+        <v>1.2989</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6686</v>
+        <v>-2.1587</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9388</v>
+        <v>-0.7563</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4621</v>
+        <v>0.9426</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4009</v>
+        <v>-1.6989</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0925</v>
+        <v>-0.4251</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.399</v>
+        <v>-0.5552</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3064</v>
+        <v>0.1301</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.3899</v>
+        <v>-1.4997</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.3899</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.688</v>
+        <v>-3.7448</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6426</v>
+        <v>-0.7416</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0454</v>
+        <v>-3.0032</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6161</v>
+        <v>-0.3116</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2415</v>
+        <v>1.7578</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.8576</v>
+        <v>-2.0694</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8598</v>
+        <v>0.6271</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2989</v>
+        <v>1.2957</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.1587</v>
+        <v>-0.6686</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7563</v>
+        <v>-0.9388</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9426</v>
+        <v>0.4621</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6989</v>
+        <v>-1.4009</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.435</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.305</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.06370000000000001</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.4554</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-3.3899</v>
+      </c>
+      <c r="W20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-1.0875</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.0875</v>
-      </c>
-      <c r="S20" t="n">
-        <v>-1.5722</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-0.8904</v>
-      </c>
-      <c r="U20" t="n">
-        <v>-0.6817</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-1.4997</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.1952</v>
-      </c>
       <c r="X20" t="n">
-        <v>-1.695</v>
+        <v>-3.3899</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7782</v>
+        <v>-5.0877</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0601</v>
+        <v>-2.3954</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.718</v>
+        <v>-2.6923</v>
       </c>
       <c r="G21" t="n">
         <v>-2.573</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4898</v>
+        <v>0.1803</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2656</v>
+        <v>-0.0697</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2242</v>
+        <v>0.2499</v>
       </c>
       <c r="V21" t="n">
         <v>-2.2599</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.832100000000001</v>
+        <v>-1.1069</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5135000000000001</v>
+        <v>-0.5134000000000007</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3186</v>
+        <v>-0.5932000000000004</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6850000000000003</v>
+        <v>-0.6850000000000005</v>
       </c>
       <c r="H22" t="n">
         <v>8.455</v>
@@ -2161,7 +2161,7 @@
         <v>-12.8416</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.350099999999999</v>
+        <v>-4.3501</v>
       </c>
       <c r="Q22" t="n">
         <v>-16.3128</v>
@@ -2170,13 +2170,13 @@
         <v>11.9628</v>
       </c>
       <c r="S22" t="n">
-        <v>3.202599999999999</v>
+        <v>6.928000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4865999999999999</v>
+        <v>-0.4867</v>
       </c>
       <c r="U22" t="n">
-        <v>3.689099999999999</v>
+        <v>7.414199999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-2.9994</v>
